--- a/assets/2026臺北數位藝術節_合作店家清冊.xlsx
+++ b/assets/2026臺北數位藝術節_合作店家清冊.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\DAF2026\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC861253-EF71-4B3B-AE72-9E8A342116F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{836A760C-DB18-4D73-89A3-F5A0541DF1FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4005" yWindow="2325" windowWidth="28740" windowHeight="19065" xr2:uid="{6CF2F47F-369B-4526-8963-C11C1554301C}"/>
+    <workbookView xWindow="-16320" yWindow="-120" windowWidth="16440" windowHeight="28320" xr2:uid="{6CF2F47F-369B-4526-8963-C11C1554301C}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="49">
   <si>
     <t>id</t>
   </si>
@@ -78,51 +78,13 @@
     <t>shop-02</t>
   </si>
   <si>
-    <t>Hyper Wave Taipei Space</t>
-  </si>
-  <si>
     <t>無</t>
   </si>
   <si>
     <t>shop-03</t>
   </si>
   <si>
-    <t>歐華酒店</t>
-  </si>
-  <si>
-    <t>The Riviera Hotel</t>
-  </si>
-  <si>
     <t>臺北市中山區新庄里吉林路456巷10號</t>
-  </si>
-  <si>
-    <t>臺北市中山區正得里南京東路一段8號4F</t>
-  </si>
-  <si>
-    <t>周一  公休
-周二  公休
-周三  12:00-19:00
-周四  12:00-19:00
-周五  12:00-19:00
-周六  12:00-19:00
-周日  公休</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">超級浪（Hyper Wave）是臺灣具有代表性的當代藝術團體，主要由洪譽豪、林思瑩、邱杰森、莫珊嵐及策展人賴佩君等多位 2020 年文化部「MIT新人推薦特區」獲選藝術家所組成。
-團隊名稱源於當代藝術的變異與不可預測性，成員們以「藝術浪人」自居，致力將當代藝術置放於各類環境與社會場景，並期許成為引領未來的「造浪者」。
-團隊在2025創立「中山科藝所」，集結展覽、研究發表、創作等功能，協助臺灣創作者與全球接軌。 </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>超級浪台北空間</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>官網：https://www.hyperwavemit.com/
-IG：https://www.instagram.com/hyperwave.mit/
-FB：https://www.facebook.com/p/%E8%B6%85%E7%B4%9A%E6%B5%AA-Hyper-Wave-100088055147550/</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">平時｜預訂制（麻糬、冷泡茶以預先訂購為主）
@@ -131,10 +93,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>0905415015</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>02-25957137</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -148,28 +106,148 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>臺北市中山區圓山里林森北路646號</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>全天營業</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>02-25853258</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">散發著普羅旺斯風情的歐華酒店（The Riviera Hotel）座落於台北市中山區，鄰近92公頃的綠地包括大佳河濱公園和台北典藏植物園。
-飯店由享譽國際的法籍建築師 Gerard Jardonnet 親自設計，巧妙融合法國布雜建築風格與東方文物線條，營造典雅舒適的別墅感。歐華酒店是台灣首家榮獲美國 LEED 綠建築白金級認證的飯店，綠意盎然的空中花園、採光極佳的中庭天井，讓旅客在繁華都市中，仍能享受被大自然環抱的體驗。 </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>emhanuel</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>官網：https://www.rivierataipei.com/</t>
+    <t>寂川</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Jyakugawa</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>臺北市中山區圓山里民族東路102號</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>周一  19:30-01:00
+周二  19:30-01:00
+周三  19:30-01:00
+周四  公休
+周五  19:30-02:00
+周六  19:30-02:00
+周日  公休</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>02-66041021</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>寂川-Jyakugawa隱身於民族橋旁，是一間主打「調酒與精緻日式小食餐酒搭」的日式餐酒館。
+日式侘寂風的店內裝潢，搭配木質吧檯與柔和燈光，讓顧客放慢腳步、品味微醺時光。除了魚子醬玉子燒、關東風貓飯等精緻家常菜，由調酒師精心研發的創意特調，牢牢鎖住顧客的味蕾。
+店內偶爾結合「池坊插花」日本美學體驗活動，讓人在充滿儀式感的環境中，體驗寂川獨有的豐富層次。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>IG：https://www.instagram.com/jyakugawa_102/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>shop-04</t>
+  </si>
+  <si>
+    <t>shop-05</t>
+  </si>
+  <si>
+    <t>拾花</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Glean Flower</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>周一  12:00-19:00
+周二  12:00-19:00
+周三  12:00-19:00
+周四  12:00-19:00
+周五  12:00-15:00
+周六  12:00-15:00
+周日  12:00-15:00</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>臺北市中山區新福里新生北路三段19巷34號</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>拾花 Glean Flower 位於新生北路巷弄內，是主打「享受有花的美好生活」的預約制花藝工作室，以「簡單、優雅、自然」作為創作核心，將花草轉化為觸手可及的日常風景。
+拾花提供多元花藝服務，包含時令鮮花、節慶花束，還承接商務空間佈置、品牌客製化花禮、結合花藝與禮品包裝等服務。
+店家引進的獨特「日本擬真花」、開設壓花相框與乾燥永生花等手作體驗課程，成為許多享受生活、講究儀式感的都市人，展現個人心意的花藝秘密基地。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gallery188</t>
+  </si>
+  <si>
+    <t>臺北市大同區至聖里承德路三段188號</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>周一  11:00-19:00
+周二  11:00-19:00
+周三  公休
+周四  公休
+周五  公休
+周六  13:00-18:00
+周日  13:00-18:00</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0966120302</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0987992335</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>官網：https://www.gleanflower.com/?srsltid=AfmBOop0q7MVJMBk3_33kdKaKbUOW4ukJ-ZPrVq9ABwc_vidGgFfoUnt
+IG：https://www.instagram.com/gleanflower/
+FB：https://www.facebook.com/gleanflower/?locale=zh_TW</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>IG：https://www.instagram.com/gallery188_/
+FB：https://www.facebook.com/p/Gallery-188%E6%9D%89%E7%95%9D%E8%97%9D%E8%A1%93-61575686574065/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>STIMLIG 原創設計家居 台北品牌店</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>STIMLIG</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>臺北市中山區新喜里德惠街165號1樓</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>周一  11:00-20:00
+周二  11:00-20:00
+周三  11:00-20:00
+周四  11:00-20:00
+周五  公休
+周六  11:00-19:00
+周日  公休</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>02-66050880</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>STIMLIG 原創設計家居台北品牌店位於德惠街巷弄內，是融合展示體驗空間、品牌設計工作室的複合空間。STIMLIG 由德文「意境（Stimmung）」與「幸福（Selig）」組成，傳遞「讓好設計走入生活」的理念。
+店內空間營造出如同藝廊般的質感家居氛圍，讓顧客體驗各國設計師及建築師團隊共同研發的原創家具。展示空間內不定期舉辦生活美學、設計相關講座活動，結合家具與生活的想像，成為城市裡找尋靈感的重要場域。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>官網：https://www.stimlig.com/taipei-design-studio/?srsltid=AfmBOoqkI-xbfDQv8g6hZn-72kt1ivILBpYVXNm4QBpIL3ohjGC3tpB3</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -591,7 +669,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F597B7B-DB6F-4918-AACF-F2DE3E6BF4FC}">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="5" max="5" width="20.375" customWidth="1"/>
@@ -637,84 +715,142 @@
         <v>10</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="D2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="H2" s="2" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="148.5">
+    <row r="3" spans="1:9" ht="165">
       <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="132">
+      <c r="A4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" s="7" t="s">
+      <c r="D4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="148.5">
-      <c r="A4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>31</v>
-      </c>
       <c r="G4" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>11</v>
       </c>
+    </row>
+    <row r="5" spans="1:9" ht="165">
+      <c r="A5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="115.5">
+      <c r="A6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
